--- a/Team-Data/2013-14/12-2-2013-14.xlsx
+++ b/Team-Data/2013-14/12-2-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,76 +728,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.474</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J2" t="n">
-        <v>81.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M2" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="N2" t="n">
         <v>0.354</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="P2" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="R2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="S2" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="V2" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="W2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="AB2" t="n">
         <v>98.7</v>
@@ -739,19 +806,19 @@
         <v>-0.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -763,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="AL2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
         <v>12</v>
@@ -772,13 +839,13 @@
         <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -793,28 +860,28 @@
         <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -930,22 +997,22 @@
         <v>24</v>
       </c>
       <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
         <v>22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
         <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>26</v>
@@ -954,7 +1021,7 @@
         <v>20</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -963,10 +1030,10 @@
         <v>14</v>
       </c>
       <c r="AR3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS3" t="n">
         <v>17</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>20</v>
@@ -993,7 +1060,7 @@
         <v>25</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1115,16 +1182,16 @@
         <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
@@ -1142,22 +1209,22 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
         <v>15</v>
       </c>
       <c r="AT4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU4" t="n">
         <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
@@ -1166,13 +1233,13 @@
         <v>22</v>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1352,19 @@
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1312,7 +1379,7 @@
         <v>29</v>
       </c>
       <c r="AM5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>29</v>
@@ -1333,7 +1400,7 @@
         <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
         <v>28</v>
@@ -1342,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
@@ -1351,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -1389,121 +1456,121 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.438</v>
+        <v>0.467</v>
       </c>
       <c r="H6" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="J6" t="n">
-        <v>82.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.434</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.793</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>33.7</v>
+        <v>33.3</v>
       </c>
       <c r="T6" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
       <c r="U6" t="n">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="V6" t="n">
         <v>16.5</v>
       </c>
       <c r="W6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>94.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
         <v>23</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
@@ -1512,34 +1579,34 @@
         <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AV6" t="n">
         <v>22</v>
       </c>
       <c r="AW6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>25</v>
@@ -1661,10 +1728,10 @@
         <v>25</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>12</v>
@@ -1682,22 +1749,22 @@
         <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU7" t="n">
         <v>27</v>
@@ -1712,7 +1779,7 @@
         <v>21</v>
       </c>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1843,13 +1910,13 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK8" t="n">
         <v>7</v>
@@ -1858,13 +1925,13 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN8" t="n">
         <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
         <v>21</v>
@@ -1879,10 +1946,10 @@
         <v>23</v>
       </c>
       <c r="AT8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
         <v>16</v>
@@ -1891,7 +1958,7 @@
         <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -2013,25 +2080,25 @@
         <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
       </c>
       <c r="AF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
         <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
         <v>4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
         <v>12</v>
@@ -2055,19 +2122,19 @@
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV9" t="n">
         <v>9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8</v>
       </c>
       <c r="AW9" t="n">
         <v>22</v>
@@ -2079,7 +2146,7 @@
         <v>20</v>
       </c>
       <c r="AZ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA9" t="n">
         <v>6</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-1.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
@@ -2219,7 +2286,7 @@
         <v>14</v>
       </c>
       <c r="AL10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM10" t="n">
         <v>20</v>
@@ -2261,16 +2328,16 @@
         <v>14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB10" t="n">
         <v>16</v>
       </c>
-      <c r="BB10" t="n">
-        <v>15</v>
-      </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2404,7 +2471,7 @@
         <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2413,7 +2480,7 @@
         <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
@@ -2422,7 +2489,7 @@
         <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2446,10 +2513,10 @@
         <v>26</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -2481,85 +2548,85 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="H12" t="n">
         <v>48.8</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
-        <v>77.8</v>
+        <v>77.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.488</v>
+        <v>0.489</v>
       </c>
       <c r="L12" t="n">
         <v>10.3</v>
       </c>
       <c r="M12" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.378</v>
+        <v>0.381</v>
       </c>
       <c r="O12" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="P12" t="n">
-        <v>32.5</v>
+        <v>33.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.703</v>
+        <v>0.704</v>
       </c>
       <c r="R12" t="n">
         <v>10.5</v>
       </c>
       <c r="S12" t="n">
-        <v>35.5</v>
+        <v>35.9</v>
       </c>
       <c r="T12" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="U12" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="V12" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X12" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>109.1</v>
+        <v>109.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,16 +2638,16 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ12" t="n">
         <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,28 +2668,28 @@
         <v>27</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
         <v>2</v>
       </c>
-      <c r="AT12" t="n">
-        <v>3</v>
-      </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -2663,85 +2730,85 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.889</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J13" t="n">
-        <v>80.3</v>
+        <v>79.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M13" t="n">
         <v>20.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.778</v>
+        <v>0.773</v>
       </c>
       <c r="R13" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S13" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W13" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X13" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="Y13" t="n">
         <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,22 +2820,22 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
         <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
         <v>14</v>
@@ -2777,28 +2844,28 @@
         <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -2923,31 +2990,31 @@
         <v>4.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>7</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
@@ -2968,7 +3035,7 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>13</v>
@@ -2977,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -3105,25 +3172,25 @@
         <v>-1.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>11</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK15" t="n">
         <v>20</v>
@@ -3135,7 +3202,7 @@
         <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
         <v>27</v>
@@ -3159,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
         <v>27</v>
@@ -3180,7 +3247,7 @@
         <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3354,25 @@
         <v>-2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>19</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>13</v>
@@ -3323,19 +3390,19 @@
         <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
@@ -3347,22 +3414,22 @@
         <v>22</v>
       </c>
       <c r="AX16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>9.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
         <v>11</v>
@@ -3496,7 +3563,7 @@
         <v>8</v>
       </c>
       <c r="AM17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
@@ -3526,7 +3593,7 @@
         <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>8</v>
@@ -3535,10 +3602,10 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>6</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3718,25 @@
         <v>-9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>28</v>
       </c>
       <c r="AG18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3690,19 +3757,19 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
         <v>29</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
         <v>25</v>
@@ -3726,7 +3793,7 @@
         <v>29</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3906,7 @@
         <v>11</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3854,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>13</v>
@@ -3872,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -3937,103 +4004,103 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.529</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>48.9</v>
+        <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>39.8</v>
+        <v>39.1</v>
       </c>
       <c r="J20" t="n">
-        <v>87</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="M20" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.413</v>
+        <v>0.407</v>
       </c>
       <c r="O20" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R20" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="S20" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42.5</v>
+        <v>41.8</v>
       </c>
       <c r="U20" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>103.8</v>
+        <v>102.1</v>
       </c>
       <c r="AC20" t="n">
         <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>9</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
@@ -4045,25 +4112,25 @@
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>12</v>
@@ -4078,16 +4145,16 @@
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
         <v>17</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -4197,22 +4264,22 @@
         <v>-6.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF21" t="n">
         <v>28</v>
       </c>
       <c r="AG21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ21" t="n">
         <v>8</v>
@@ -4221,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4254,10 +4321,10 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -4269,7 +4336,7 @@
         <v>27</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE22" t="n">
         <v>6</v>
@@ -4391,13 +4458,13 @@
         <v>5</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>14</v>
       </c>
       <c r="AK22" t="n">
         <v>11</v>
@@ -4424,16 +4491,16 @@
         <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
         <v>13</v>
@@ -4448,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -4483,124 +4550,124 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.353</v>
+        <v>0.375</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.9</v>
       </c>
       <c r="J23" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="L23" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="M23" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.374</v>
+        <v>0.382</v>
       </c>
       <c r="O23" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P23" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.761</v>
+        <v>0.754</v>
       </c>
       <c r="R23" t="n">
         <v>9.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="V23" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="W23" t="n">
         <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>98.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.6</v>
+        <v>-1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
         <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
         <v>8</v>
       </c>
       <c r="AL23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP23" t="n">
         <v>23</v>
       </c>
-      <c r="AP23" t="n">
-        <v>24</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4609,35 +4676,35 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU23" t="n">
         <v>17</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>19</v>
       </c>
       <c r="AV23" t="n">
         <v>27</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
         <v>19</v>
       </c>
       <c r="AY23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC23" t="n">
         <v>18</v>
       </c>
-      <c r="BC23" t="n">
-        <v>21</v>
-      </c>
       <c r="BD23" t="n">
         <v>10</v>
       </c>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>22</v>
@@ -4758,7 +4825,7 @@
         <v>2</v>
       </c>
       <c r="AI24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
         <v>2</v>
@@ -4779,7 +4846,7 @@
         <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4794,7 +4861,7 @@
         <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>29</v>
@@ -4803,19 +4870,19 @@
         <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC24" t="n">
         <v>27</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4940,10 +5007,10 @@
         <v>15</v>
       </c>
       <c r="AI25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
         <v>6</v>
@@ -4970,7 +5037,7 @@
         <v>23</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>21</v>
@@ -4985,7 +5052,7 @@
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
         <v>3</v>
@@ -4994,7 +5061,7 @@
         <v>16</v>
       </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -5029,85 +5096,85 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.833</v>
+        <v>0.824</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J26" t="n">
-        <v>85</v>
+        <v>85.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
       <c r="O26" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="P26" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.805</v>
+        <v>0.799</v>
       </c>
       <c r="R26" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="S26" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T26" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U26" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="V26" t="n">
         <v>14.2</v>
       </c>
       <c r="W26" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="X26" t="n">
         <v>4.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z26" t="n">
         <v>19.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -5119,13 +5186,13 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
@@ -5134,31 +5201,31 @@
         <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AN26" t="n">
         <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>4</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -5289,25 +5356,25 @@
         <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI27" t="n">
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
@@ -5322,10 +5389,10 @@
         <v>22</v>
       </c>
       <c r="AO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -5340,7 +5407,7 @@
         <v>22</v>
       </c>
       <c r="AU27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5352,13 +5419,13 @@
         <v>30</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.833</v>
+        <v>0.824</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.491</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
         <v>12.7</v>
@@ -5432,34 +5499,34 @@
         <v>16.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="T28" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="U28" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="V28" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
         <v>17.8</v>
@@ -5468,10 +5535,10 @@
         <v>101.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,25 +5550,25 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,31 +5577,31 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY28" t="n">
         <v>12</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -5653,25 +5720,25 @@
         <v>-0.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG29" t="n">
         <v>21</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>26</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
         <v>27</v>
@@ -5707,7 +5774,7 @@
         <v>30</v>
       </c>
       <c r="AV29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -5757,127 +5824,127 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>0.211</v>
+        <v>0.167</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
       <c r="J30" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.432</v>
+        <v>0.426</v>
       </c>
       <c r="L30" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="M30" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.322</v>
+        <v>0.308</v>
       </c>
       <c r="O30" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P30" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.719</v>
+        <v>0.715</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U30" t="n">
         <v>19.3</v>
       </c>
       <c r="V30" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="W30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>91.5</v>
+        <v>90.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF30" t="n">
         <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>28</v>
       </c>
       <c r="AJ30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="n">
         <v>27</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
         <v>23</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
         <v>30</v>
@@ -5892,25 +5959,25 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX30" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="H31" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I31" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
       <c r="J31" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.447</v>
@@ -5966,76 +6033,76 @@
         <v>9</v>
       </c>
       <c r="M31" t="n">
-        <v>22.5</v>
+        <v>23.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.739</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S31" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U31" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W31" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
         <v>4.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
         <v>18</v>
@@ -6044,25 +6111,25 @@
         <v>6</v>
       </c>
       <c r="AM31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP31" t="n">
         <v>25</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>22</v>
       </c>
       <c r="AQ31" t="n">
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AT31" t="n">
         <v>23</v>
@@ -6074,10 +6141,10 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
@@ -6089,10 +6156,10 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-2-2013-14</t>
+          <t>2013-12-02</t>
         </is>
       </c>
     </row>
